--- a/PTBR/Lang/PTBR/Game/Word.xlsx
+++ b/PTBR/Lang/PTBR/Game/Word.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Destruído</t>
+          <t>destroçado</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mutilado</t>
+          <t>mutilado</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inocente</t>
+          <t>inocente</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ateu</t>
+          <t>ateu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Preguiçoso</t>
+          <t>preguiça</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Extinto</t>
+          <t>extinto</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trapaceiro</t>
+          <t>trapaceiro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aleijado</t>
+          <t>aleijado</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Virtuoso</t>
+          <t>virtuoso</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Covarde</t>
+          <t>covarde</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Imundo</t>
+          <t>camarada</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Herege</t>
+          <t>herético</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sangue-Frio</t>
+          <t>sangue-frio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bêbado</t>
+          <t>bêbado</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Merda</t>
+          <t>merda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pervertido</t>
+          <t>pervertido</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atraente</t>
+          <t>atraente</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Celebridade, Famoso</t>
+          <t>celebridade,famoso</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prostituta, Vadia</t>
+          <t>vadia,cadela</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estranho</t>
+          <t>estranho</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inútil</t>
+          <t>inútil</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Belo</t>
+          <t>belo</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Astuto</t>
+          <t>astuto</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Louco</t>
+          <t>louco</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grande, Grandioso</t>
+          <t>grande,grandioso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sujo, Imundo, Negro</t>
+          <t>sujo,imundo,preto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Limpo</t>
+          <t>limpo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Desperto</t>
+          <t>desperto</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Furioso</t>
+          <t>enfurecido</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Novíssimo, Novo</t>
+          <t>novinho,novo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Puro, Branco</t>
+          <t>puro,branco</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nobre</t>
+          <t>nobre</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sem Nome</t>
+          <t>sem nome</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Doente</t>
+          <t>doente</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alegre</t>
+          <t>alegre</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Misericordioso</t>
+          <t>misericordioso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Agonizante</t>
+          <t>moribundo</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Justo</t>
+          <t>justo</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sombrio</t>
+          <t>sombrio</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inteligente</t>
+          <t>esperto</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Angelical</t>
+          <t>angelical</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Resistente</t>
+          <t>durão</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ciumento</t>
+          <t>ciumento</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rancoroso</t>
+          <t>ranzinza</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Orgulhoso</t>
+          <t>orgulhoso</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gentil</t>
+          <t>gentil</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Triste</t>
+          <t>triste</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Desesperado</t>
+          <t>desesperado</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Quieto</t>
+          <t>quieto</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Melancólico</t>
+          <t>melancólico</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Masoquista</t>
+          <t>masoquista</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cruel</t>
+          <t>cruel</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Agressivo</t>
+          <t>agressivo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Narcisista</t>
+          <t>narcisista</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Maligno</t>
+          <t>maligno</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bom</t>
+          <t>bom</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Delicado</t>
+          <t>meigo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Arrogante</t>
+          <t>arrogante</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Profundo</t>
+          <t>profundo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vingativo</t>
+          <t>vingativo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Amoroso</t>
+          <t>amoroso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tranquilo</t>
+          <t>tranquilo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Calmo</t>
+          <t>calmo</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sereno</t>
+          <t>sereno</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Amigável</t>
+          <t>amigável</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fofo</t>
+          <t>fofo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reto</t>
+          <t>reto</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Doce</t>
+          <t>doce</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Azul</t>
+          <t>azul</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ardente</t>
+          <t>flamejante</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>solene</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Velho</t>
+          <t>velho</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Exilado</t>
+          <t>exilado</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Unido</t>
+          <t>unido</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ofensivo</t>
+          <t>ofensivo</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Repleto</t>
+          <t>cheio</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Curador</t>
+          <t>curativo</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brilhante</t>
+          <t>reluzente</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Corrupto</t>
+          <t>corrupto</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Insano</t>
+          <t>doido</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Inteligente</t>
+          <t>inteligente</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Faminto</t>
+          <t>faminto</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Prestativo</t>
+          <t>prestativo</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Encantador</t>
+          <t>encantador</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Honesto</t>
+          <t>honesto</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Amável</t>
+          <t>simpático</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Furioso</t>
+          <t>frenético</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Majestoso</t>
+          <t>majestoso</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Vermelho</t>
+          <t>vermelho</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Preto</t>
+          <t>preto</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Verde</t>
+          <t>verde</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>branco</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Roxo</t>
+          <t>roxo</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Congelante</t>
+          <t>congelante</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Perigoso</t>
+          <t>perigoso</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Corajoso</t>
+          <t>valente</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Errante</t>
+          <t>andarilho</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Típico</t>
+          <t>típico</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Podre</t>
+          <t>podre</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ambicioso</t>
+          <t>ambicioso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Esperançoso</t>
+          <t>esperançoso</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Luxurioso</t>
+          <t>libidinoso</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Teimoso</t>
+          <t>teimoso</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Deslumbrante</t>
+          <t>de tirar o fôlego</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Capaz</t>
+          <t>capaz</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dependente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Divino</t>
+          <t>divino</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fértil, Empolgado</t>
+          <t>no cio,excitado</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Gordinho</t>
+          <t>rechonchudo</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Suave</t>
+          <t>macio</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Precioso</t>
+          <t>precioso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Apático</t>
+          <t>apático</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Entediado</t>
+          <t>entediado</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Antigo</t>
+          <t>ancestral</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Impassível</t>
+          <t>de cara fechada</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Travesso</t>
+          <t>maroto</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tentáculo</t>
+          <t>tentáculo</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Quebrado</t>
+          <t>quebrado</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Estúpido</t>
+          <t>tolo</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ex</t>
+          <t>antigo</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fofinho</t>
+          <t>fofo</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ex-Multinacional</t>
+          <t>ex-empresa global</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Atrevido</t>
+          <t>atrevido</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Nervoso</t>
+          <t>nervoso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Encurralado</t>
+          <t>encurralado</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Monstruoso</t>
+          <t>monstruoso</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Trabalhador</t>
+          <t xml:space="preserve">trabalhador </t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Apaixonado</t>
+          <t>apaixonado</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sábio</t>
+          <t>sábio</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Manipulador</t>
+          <t>maquiavélico</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Maternal</t>
+          <t>materno</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Insistente, Fácil De Persuadir</t>
+          <t>insistente,influenciável</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Fraco De Vontade</t>
+          <t>fraco de vontade</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tentador</t>
+          <t>tentador</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Altruísta</t>
+          <t>abnegado</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Enganado, Trapaceado</t>
+          <t>enganado,traído</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Desesperançado</t>
+          <t>sem esperança</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Corno, Traído</t>
+          <t>chifrudo,enganado</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cantor</t>
+          <t>cantante</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Nobre</t>
+          <t>nobre</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Camponês, Agricultor</t>
+          <t>camponês,agricultor</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Idiota</t>
+          <t>idiota</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Companheiro</t>
+          <t>camarada</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Aventureiro</t>
+          <t>aventureiro</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Andarilho</t>
+          <t>andarilho</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Viajante</t>
+          <t>viajante</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Criminoso</t>
+          <t>criminoso</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Pecador</t>
+          <t>pecador</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Mendigo</t>
+          <t>mendigo</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ermitão</t>
+          <t>eremita</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Sábio</t>
+          <t>sábio</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>animal</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Monstro</t>
+          <t>monstro</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Sofredor</t>
+          <t>sofredor</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Canalha</t>
+          <t>escória</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Vadia, Prostituta</t>
+          <t>cadela,vadia</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Santo</t>
+          <t>santo</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Fantasma</t>
+          <t>fantasma</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Espírito</t>
+          <t>espírito</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Colono</t>
+          <t>colono</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Dama</t>
+          <t>dama</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Menina</t>
+          <t>garotinha</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Sacerdote</t>
+          <t>sacerdote</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Salvador</t>
+          <t>salvador</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Garota Jovem</t>
+          <t>moça</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Garoto Jovem</t>
+          <t>moço</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Poeta</t>
+          <t>poeta</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Dançarino</t>
+          <t>dançarino</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Curandeiro</t>
+          <t>curandeiro</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Planta</t>
+          <t>planta</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Erudito</t>
+          <t>estudioso</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Pedregulho</t>
+          <t>seixo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bêbado</t>
+          <t>bêbado</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Guerreiro</t>
+          <t>guerreiro</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cavaleiro</t>
+          <t>cavaleiro</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Espião</t>
+          <t>espião</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Assassino</t>
+          <t>assassino</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Escravo</t>
+          <t>escravo</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Mago</t>
+          <t>mago</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bruxa</t>
+          <t>bruxa</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Ladrão</t>
+          <t>ladrão</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Mercenário</t>
+          <t>bandido</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bardo</t>
+          <t>bardo</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bárbaro Furioso</t>
+          <t>berserker</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Mineiro</t>
+          <t>mineiro</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Herói</t>
+          <t>herói</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Campeão</t>
+          <t>campeão</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Caçador</t>
+          <t>caçador</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Monge</t>
+          <t>monge</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Pirata</t>
+          <t>pirata</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Buscador</t>
+          <t>buscador</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Mercenário</t>
+          <t>mercenário</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Defensor</t>
+          <t>defensor</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Usurpador</t>
+          <t>usurpador</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Alquimista</t>
+          <t>alquimista</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bárbaro</t>
+          <t>bárbaro</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Profeta</t>
+          <t>profeta</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Batedor</t>
+          <t>batedor</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Traidor</t>
+          <t>traidor</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Mercador</t>
+          <t>mercador</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Pastor</t>
+          <t>pastor</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Paladino</t>
+          <t>paladino</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Patrulheiro</t>
+          <t>patrulheiro</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Necromante</t>
+          <t>necromante</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>professor</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Anjo</t>
+          <t>anjo</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Demônio, Diabo</t>
+          <t>demônio,diabo</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Exilado</t>
+          <t>exilado</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Arqueiro</t>
+          <t>arqueiro</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Duelista</t>
+          <t>duelista</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Herege</t>
+          <t>herege</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Espadachim</t>
+          <t>espadachim</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Ferreiro</t>
+          <t>ferreiro</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Marinheiro</t>
+          <t>marinheiro</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Soldado</t>
+          <t>soldado</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Máquina</t>
+          <t>máquina</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Querido</t>
+          <t>querido</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Viúva</t>
+          <t>viúva</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Arqueólogo</t>
+          <t>arqueólogo</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Homem</t>
+          <t>homem</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Mulher</t>
+          <t>mulher</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Vampiro</t>
+          <t>vampiro</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Donzela</t>
+          <t>donzela</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Dispositivo Mágico</t>
+          <t>dispositivo mágico</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bastardo</t>
+          <t>bastardo</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Menino</t>
+          <t>garoto</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Menina</t>
+          <t>garota</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>O Vazio</t>
+          <t>o vazio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Algum Lugar</t>
+          <t>algum lugar</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Uma Floresta Profunda</t>
+          <t>uma floresta profunda</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Uma Montanha</t>
+          <t>uma montanha</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Uma Vila Triste</t>
+          <t>uma vila triste</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Um Paraíso</t>
+          <t>um paraíso</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Uma Área Rural</t>
+          <t>uma área rural</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Uma Vila Isolada</t>
+          <t>uma vila isolada</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Uma Terra Abandonada</t>
+          <t>uma terra abandonada</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Uma Terra Esquecida</t>
+          <t>uma terra esquecida</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Um Ermo</t>
+          <t>uma terra árida</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Um Local Proibido</t>
+          <t>um lugar proibido</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>O Vale Da Dor</t>
+          <t>o Vale da Tristeza</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Norte De Tyris</t>
+          <t>Tyris do Norte</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Sul De Tyris</t>
+          <t>Tyris do Sul</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Uma Terra Estrangeira</t>
+          <t>uma terra estrangeira</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>O Leste</t>
+          <t>o leste</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>O Oeste</t>
+          <t>o oeste</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Uma Cidade Vibrante</t>
+          <t>uma cidade animada</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Caverna</t>
+          <t>caverna</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Igreja</t>
+          <t>igreja</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>casa</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Casa Abandonada</t>
+          <t>casa abandonada</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Rua</t>
+          <t>rua</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Lixão</t>
+          <t>área de lixo</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Estalagem</t>
+          <t>estalagem</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Beira Do Rio</t>
+          <t>beira do rio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Porão</t>
+          <t>porão</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Lugar Escuro</t>
+          <t>lugar escuro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Armazém</t>
+          <t>armazém</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Cemitério</t>
+          <t>cemitério</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Celeiro</t>
+          <t>celeiro</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Poço</t>
+          <t>poço</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Barril</t>
+          <t>barril</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Banheiro</t>
+          <t>banheiro</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Prisão</t>
+          <t>cadeia</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Parque</t>
+          <t>parque</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>porto</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Sombra De Árvore</t>
+          <t>sombra da árvore</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Bordel</t>
+          <t>bordel</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Beco</t>
+          <t>beco</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Arbusto</t>
+          <t>arbusto</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Jardim</t>
+          <t>jardim</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>torre</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Ninho De Pássaro</t>
+          <t>ninho de pássaro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Cama De Palha</t>
+          <t>cama de palha</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Quadrado Mágico</t>
+          <t>círculo mágico</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Oficina</t>
+          <t>oficina</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Laboratório</t>
+          <t>laboratório</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Circo</t>
+          <t>circo</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Ruína</t>
+          <t>ruínas</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Cinzas</t>
+          <t>cinzas</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Praça</t>
+          <t>praça</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Matadouro</t>
+          <t>matadouro</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Altar</t>
+          <t>altar</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Forca</t>
+          <t>forca</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Esgoto</t>
+          <t>esgoto</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Prisão</t>
+          <t>prisão</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Manicômio</t>
+          <t>asilo</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Vila</t>
+          <t>casarão</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Abrigo</t>
+          <t>abrigo</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Necrotério</t>
+          <t>necrotério</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Esconderijo</t>
+          <t>esconderijo</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Abismo</t>
+          <t>abismo</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Lugar Assustador</t>
+          <t>lugar assustador</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Lugar Perigoso</t>
+          <t>lugar perigoso</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Sítio Histórico</t>
+          <t>sítio histórico</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Mosteiro</t>
+          <t>mosteiro</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Capela</t>
+          <t>capela</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Estalagem, Taverna</t>
+          <t>estalagem,taberna</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Reino, Império, Nação</t>
+          <t>reino,império,nação</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Seguidores, Reunião</t>
+          <t>seguidores,congregação</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Vila</t>
+          <t>vila</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Cidade</t>
+          <t>cidade</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Lar</t>
+          <t>lar</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Jardim</t>
+          <t>jardim</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Círculo</t>
+          <t>círculo</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Clã, Família</t>
+          <t>clã,família</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>lar</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Terra Natal</t>
+          <t>terra natal</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Solo, Ninho</t>
+          <t>toca,ninho</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Dimensão, Domínio</t>
+          <t>dimensão,domínio</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Exército, Trupe, Companhia</t>
+          <t>exército,trupe,companhia</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Propriedade, Distrito</t>
+          <t>propriedade,distrito</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Ducado, Linhagem, República</t>
+          <t>ducado,dinastia,república</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Castelo, Torre, Fortaleza</t>
+          <t>castelo,torre,fortaleza</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Céu, Guarida, Bordel, Habitat</t>
+          <t>paraíso,covil,bordel,habitat</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Terra Das Maravilhas, Éden, Sião</t>
+          <t>país das maravilhas,paraíso,terra prometida</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Porão, Esconderijo</t>
+          <t>porão,esconderijo</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Esconderijo</t>
+          <t>esconderijo</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Ateliê, Bar</t>
+          <t>ateliê,boteco</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Lagoa, Lago, Pântano</t>
+          <t>lagoa,lago,pântano</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>País, Reino</t>
+          <t>país,reino</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>domínio</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Fazenda, Campo</t>
+          <t>fazenda,campo</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Federação, União</t>
+          <t>federação,união</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Clube, Salão, Círculo</t>
+          <t>clube,salão,círculo</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Colônia, Comuna, Oásis</t>
+          <t>colônia,comuna,oásis</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>academia</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Meca, Santuário</t>
+          <t>meca,santuário</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Gangue, Assaltantes, Matilha</t>
+          <t>gangue,bandidos,matilha</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Festa, Bando</t>
+          <t>grupo,bando</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Buraco, Chalé, Casa</t>
+          <t>toca,chalé,casa</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Santuário</t>
+          <t>santuário</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Abrigo, Habitação, Esconderijo</t>
+          <t>poleiro,morada,esconderijo</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Mundo, Terra, Sociedade</t>
+          <t>mundo,terra,sociedade</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Retiro, Toca, Vila</t>
+          <t>refúgio,toca,casarão</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Morada, Guarida, Asas, Pena, Lar, Vela</t>
+          <t>moradia,covil,asas,pena,lar,vela</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Esperança, Luz</t>
+          <t>esperança,luz</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Amigo, Tropa, Enxame</t>
+          <t>amigo,companhia,enxame</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Horda, Rebanho, Bando</t>
+          <t>horda,manada,matilha</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Multidão, Remanescente, Sobreviventes</t>
+          <t>turba,restos,sobreviventes</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Sala, Classe</t>
+          <t>sala,classe</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Linhagem, Descendência, Descendente</t>
+          <t>linhagem,descendência,descendente</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Juramento, Voto</t>
+          <t>juramento,voto</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Irmandade, Irmãos, Irmãs</t>
+          <t>irmandade,irmãos,irmãs</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Povo, Crianças</t>
+          <t>povo,crianças</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Culto, Ordem, Ensinamento</t>
+          <t>culto,ordem,doutrina</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Guilda</t>
+          <t>guilda</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Missionários, Seita, Cultistas</t>
+          <t>missionários,culto,cultistas</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Facção, Grupo, Esquadrão</t>
+          <t>facção,grupo,esquadrão</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Cavalaria, Força Armada</t>
+          <t>cavalaria,força armada</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Cavaleiros</t>
+          <t>cavaleiros</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Defensores, Cantores</t>
+          <t>defensores,cantores</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Templo, Igreja, Mosteiro</t>
+          <t>templo,igreja,mosteiro</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Refúgio, Estância, Esconderijo</t>
+          <t>refúgio,retiro,abrigo</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Santuário, Acampamento, Asilo</t>
+          <t>porto seguro,acampamento,asilo</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Abrigo</t>
+          <t>abrigo</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Castelo, Mansão, Sobrado</t>
+          <t>château,mansão,solar</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Terroristas, Rebelde, Resistência</t>
+          <t>terroristas,rebelde,resistência</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Região, Secreto, Arcádia, Paraíso</t>
+          <t>região,segredo,arcádia,paraíso</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Paraíso, Céu, Terra Dos Sonhos, Hotel, Terra Das Fadas</t>
+          <t>paraíso,céu,terra dos sonhos,hotel,terra das fadas</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Estalagem</t>
+          <t>estalagem</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Lei</t>
+          <t>lei</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Desgraça, Tormento</t>
+          <t>condenação,tormento</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>restaurante</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Pastagem, Curral</t>
+          <t>pasto,engorda</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Orgulho, Maldição, Pecado, Valor</t>
+          <t>orgulho,maldição,pecado,valor</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Pai, Mãe, Filho, Filha, Crianças, Criança</t>
+          <t>pai,mãe,filho,filha,filhos,criança</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Lenda, Contos</t>
+          <t>lenda,causos</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Laço, Promessa, Contrato, Lágrimas</t>
+          <t>laço,promessa,contrato,lágrimas</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Vale, Floresta, Colina</t>
+          <t>vale,floresta,colina</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Vento, Córrego, Tempestade, Tormenta</t>
+          <t>vento,riacho,tempestade,tormenta</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Matilha, Enxame, Multidão, Bando, Horda, Mob, Ninho</t>
+          <t>matilha,enxame,multidão,bando,horda,turma,ninho</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Minha Mãezinha</t>
+          <t>老妈</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Vossa Majestade</t>
+          <t>Sua Majestade</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Revelador</t>
+          <t>启示者</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Capitão</t>
+          <t>Mestre</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Senhor das Águas</t>
+          <t>主人</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Chefe</t>
+          <t>Patrão</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Cadela</t>
+          <t>Vadia</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Galinha</t>
+          <t>Frango</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Lixo</t>
+          <t>Traste</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Filho do Céu</t>
+          <t>天子</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Imperador Celestial</t>
+          <t>天帝</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Chefe</t>
+          <t>首领</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>O Bravo</t>
+          <t>O Valente</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Sênior</t>
+          <t>Ancião</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Almirante De Merda</t>
+          <t>Almirante de Merda</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Vossa Alteza</t>
+          <t>Sua Alteza</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Papai</t>
+          <t>Paizinho</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Velho</t>
+          <t>Coroa</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Bruxa Velha</t>
+          <t>Velha Corja</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Meu Precioso</t>
+          <t>Meu precioso</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Herói Da Luz</t>
+          <t>Herói da Luz</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -12523,12 +12523,12 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Escolhido</t>
+          <t>O Escolhido</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Choosen one</t>
+          <t>Chosen one</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Viajante Dos Céus</t>
+          <t>Viajante dos Céus</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>O Viajante Dos Céus</t>
+          <t>O Viajante dos Céus</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Marido</t>
+          <t>Maridinho</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Viajante Solitário</t>
+          <t>Andarilho Solitário</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Mensageiro</t>
+          <t>Entregador</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Portador</t>
+          <t>Mensageiro</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Demônio</t>
+          <t>Diabo</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Satanás</t>
+          <t>Satan</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Filhote De Gato</t>
+          <t>Filhote de Gato</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Filhote De Cachorro</t>
+          <t>Cachorrinho</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Cachorro</t>
+          <t>Cão</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Rancho</t>
+          <t>rancho</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Pastagem</t>
+          <t>pasto</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Fazenda, Casa De Criação</t>
+          <t>fazenda,casa de criação</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Laticínio</t>
+          <t>laticínio</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
